--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象適應</t>
+          <t xml:space="preserve">傷害緩衝</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌈</t>
+          <t xml:space="preserve">🌫️</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemRes</t>
+          <t xml:space="preserve">globalDmgRed</t>
         </is>
       </c>
       <c r="G25">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">全屬性抗性額外提高</t>
+          <t xml:space="preserve">全局減傷額外提高</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -76,6 +76,46 @@
           <t xml:space="preserve">說明</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潛力類型</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷卻</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎值</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傷害類型</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持續秒</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機制</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英文名</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風味</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -894,16 +934,6 @@
       <c r="J21">
         <v>3</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目前暫不開放升級</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">解鎖新類型技能「潛力」三個並給予技能點</t>
@@ -1317,16 +1347,6 @@
       <c r="J31">
         <v>3</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目前暫不開放升級</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">解鎖新類型技能「潛力」三個並給予技能點</t>
@@ -2355,16 +2375,6 @@
       <c r="J56">
         <v>3</v>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目前暫不開放升級</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">解鎖新類型技能「潛力」三個並給予技能點</t>
@@ -3393,16 +3403,6 @@
       <c r="J81">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目前暫不開放升級</t>
-        </is>
-      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">解鎖新類型技能「潛力」一個並給予技能點</t>
@@ -3417,30 +3417,51 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">p1_time</t>
+          <t xml:space="preserve">velocityForce</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">時空折疊</t>
+          <t xml:space="preserve">極速之力</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">⏳</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialCdr</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="I82">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">每級使所有技能的冷卻時間額外縮短 1%</t>
+          <t xml:space="preserve">突破速度的極限——你的攻速自此掙脫 5 次/秒的枷鎖，直抵無限，能登臨何等境界，端看你的領悟。每級 +5% 攻速加成。</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="O82">
+        <v>60</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspd</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Velocity Force</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">突破速度極限，攻速掙脫 5 次/秒的枷鎖，能達到什麼程度端看你的領悟。</t>
         </is>
       </c>
     </row>
@@ -3452,30 +3473,59 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">p2_secondLife</t>
+          <t xml:space="preserve">lightningOverdrive</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">第二命題</t>
+          <t xml:space="preserve">雷霆過載</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">💫</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialRevive</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">每場戰鬥第一次受到致命傷害時復活，並恢復最大生命值的 20%（最高 100%）</t>
+          <t xml:space="preserve">雷霆過載，化為狂亂的連鎖閃電——雷電技能 100% 引動雷鏈，於敵群間肆意躍動（最多 3＋連擊數 次彈跳、每次撕裂 10% 該擊傷害），愈戰愈烈、生生不息，持續 8 秒。每級 +0.4% 雷電傷害。</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="O83">
+        <v>45</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="R83">
+        <v>8</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainLightning</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lightning Overdrive</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">過載的雷能在敵群間肆意跳躍，愈是激烈愈難止息。</t>
         </is>
       </c>
     </row>
@@ -3487,30 +3537,54 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">p3_lootEcho</t>
+          <t xml:space="preserve">chronoCollapse</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">掉落回聲</t>
+          <t xml:space="preserve">時間坍縮</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">🎁</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialLootDup</t>
+          <t xml:space="preserve">🕳️</t>
         </is>
       </c>
       <c r="I84">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">每級使掉落物數量額外增加 5%</t>
+          <t xml:space="preserve">打破時空的禁錮——冷卻縮減自此突破 60% 的天塹，所有技能的冷卻如坍縮的星辰般急速消融，持續 3 秒。每級額外 −0.2% 冷卻。（不縮減自身冷卻，但仍受一般冷卻縮減加成）</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="O84">
+        <v>75</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>3</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cdrUncap</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chronostasis</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">此技能對自身冷卻不生效，但冷卻縮減仍可作用於它。</t>
         </is>
       </c>
     </row>
@@ -3522,40 +3596,51 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4_voidBag</t>
+          <t xml:space="preserve">absoluteSanctuary</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛空背包</t>
+          <t xml:space="preserve">絕對領域</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">🎒</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialInvCap</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="I85">
-        <v>100</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目前暫不開放升級</t>
-        </is>
+        <v>0.025</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">每級增加 100 格背包容量</t>
+          <t xml:space="preserve">降臨絕對的領域，展開無敵結界——其間免疫一切傷害與負面效果，任何攻擊都無法觸及你分毫。基礎 0.5 秒，每級 +0.025 秒。</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="O85">
+        <v>75</v>
+      </c>
+      <c r="P85">
+        <v>0.5</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">invuln</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Absolute Sanctuary</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在絕對的領域中，任何傷害都無法觸及你分毫。</t>
         </is>
       </c>
     </row>
@@ -3567,40 +3652,51 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5_elementCore</t>
+          <t xml:space="preserve">lastStandUndying</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">元素核心</t>
+          <t xml:space="preserve">不屈意志</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔆</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialElemAtk</t>
+          <t xml:space="preserve">💀</t>
         </is>
       </c>
       <c r="I86">
-        <v>2</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目前暫不開放升級</t>
-        </is>
+        <v>0.4</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">每級使所有元素附加傷害額外提高 2%</t>
+          <t xml:space="preserve">意志不屈者，縱使命懸一線亦絕不倒下——受到致命傷害時免除死亡，並獲得 1 秒無敵。觸發後進入冷卻，每級 −0.4 秒。（不受冷卻縮減影響）</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">passiveTrigger</t>
+        </is>
+      </c>
+      <c r="O86">
+        <v>90</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undyingGuard</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last Undying Stand</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">意志不屈者，縱使命懸一線也絕不倒下。（此技能不受冷卻縮減影響）</t>
         </is>
       </c>
     </row>
@@ -3612,30 +3708,54 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6_execution</t>
+          <t xml:space="preserve">timeBarrier</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">終焉預言</t>
+          <t xml:space="preserve">時間結界</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialExecute</t>
+          <t xml:space="preserve">⏱️</t>
         </is>
       </c>
       <c r="I87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">目標生命低於 20% 時，每級使造成的傷害額外提高 2%</t>
+          <t xml:space="preserve">編織拖曳時光的結界，敵人的動作被無情延緩，攻速大幅降低，持續 8 秒。每級敵人攻速 −1%。（敵降低後攻速 = 原攻速 /(1+降低%)）</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="O87">
+        <v>45</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>8</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemySlow</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Barrier</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">結界之內，敵人的時間被無情拖曳。</t>
         </is>
       </c>
     </row>
@@ -3647,30 +3767,48 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7_aegis</t>
+          <t xml:space="preserve">dualCoreFusion</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">護盾轉生</t>
+          <t xml:space="preserve">混沌雙修</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪞</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialShieldOverflow</t>
+          <t xml:space="preserve">☯️</t>
         </is>
       </c>
       <c r="I88">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">每級將溢出護盾的 5% 轉換為生命回復</t>
+          <t xml:space="preserve">雙核交融，物理與魔法的界限就此崩解——所有物理技能汲取魔攻之力、所有魔法技能承載物攻之威。每級 +0.6%。</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">passive</t>
+        </is>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crossCore</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dual-Core Fusion</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雙核交融，物理與魔法在你手中不再涇渭分明。</t>
         </is>
       </c>
     </row>
@@ -3682,30 +3820,56 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8_manaLoop</t>
+          <t xml:space="preserve">omegaImpact</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">法力迴圈</t>
+          <t xml:space="preserve">必殺一擊</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔄</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialManaRefund</t>
+          <t xml:space="preserve">🎯</t>
         </is>
       </c>
       <c r="I89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">技能命中敵人後，每級返還技能消耗法力的 2%</t>
+          <t xml:space="preserve">凝聚全身之力於一擊，依你的爆擊率轟出毀天滅地的必殺——造成「爆擊率% × 必殺傷害加成%」的物理傷害；爆擊率愈高，此擊愈是無可匹敵。必殺傷害加成 = 100% + 每級 +3%。</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="O89">
+        <v>60</v>
+      </c>
+      <c r="P89">
+        <v>100</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omega</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega Impact</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爆擊率愈高，這一擊便愈是毀天滅地。</t>
         </is>
       </c>
     </row>
@@ -3717,30 +3881,54 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">p9_towerClock</t>
+          <t xml:space="preserve">sacredInversion</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">高塔時鐘</t>
+          <t xml:space="preserve">聖療逆轉</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗼</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialTowerTime</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">每級增加高塔挑戰限時 1 秒</t>
+          <t xml:space="preserve">聖療之光賜福於身，生命與法力回復大幅提升；滿溢的療癒之力逆轉為裁決，化作同等傷害傾瀉於敵，持續 6 秒。每級 +0.5%。</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="O90">
+        <v>45</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>6</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacredInvert</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sacred Inversion</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">滿溢的聖光既能療癒自身，亦能化為裁決敵人的利刃。</t>
         </is>
       </c>
     </row>
@@ -3752,30 +3940,54 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10_offlineOracle</t>
+          <t xml:space="preserve">chronosStasis</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">離線預言</t>
+          <t xml:space="preserve">時空凝滯</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌙</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">potentialOffline</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="I91">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">每級使離線收益額外提高 5%</t>
+          <t xml:space="preserve">封鎖周遭的時空，令萬物靜止——唯有承神之賜福者能自由行動；凝滯之間你的所有傷害大幅提升，敵人動彈不得，持續 8 秒。每級 +0.5% 所有傷害。</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="O91">
+        <v>120</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>8</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timeStop</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chronos Stasis</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">唯有獲得神之賜福者，方能在凝滯的時空中行動自如。</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -3440,11 +3440,8 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="O82">
-        <v>60</v>
+          <t xml:space="preserve">passive</t>
+        </is>
       </c>
       <c r="P82">
         <v>0</v>

--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -76,46 +76,6 @@
           <t xml:space="preserve">說明</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力類型</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冷卻</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">基礎值</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">傷害類型</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">持續秒</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">機制</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">英文名</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">風味</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3406,585 +3366,6 @@
       <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">解鎖新類型技能「潛力」一個並給予技能點</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">velocityForce</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">極速之力</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚡</t>
-        </is>
-      </c>
-      <c r="I82">
-        <v>5</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">突破速度的極限——你的攻速自此掙脫 5 次/秒的枷鎖，直抵無限，能登臨何等境界，端看你的領悟。每級 +5% 攻速加成。</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">passive</t>
-        </is>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspd</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Velocity Force</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">突破速度極限，攻速掙脫 5 次/秒的枷鎖，能達到什麼程度端看你的領悟。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lightningOverdrive</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雷霆過載</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🌩️</t>
-        </is>
-      </c>
-      <c r="I83">
-        <v>0.4</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雷霆過載，化為狂亂的連鎖閃電——雷電技能 100% 引動雷鏈，於敵群間肆意躍動（最多 3＋連擊數 次彈跳、每次撕裂 10% 該擊傷害），愈戰愈烈、生生不息，持續 8 秒。每級 +0.4% 雷電傷害。</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="O83">
-        <v>45</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="R83">
-        <v>8</v>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chainLightning</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lightning Overdrive</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">過載的雷能在敵群間肆意跳躍，愈是激烈愈難止息。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chronoCollapse</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">時間坍縮</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🕳️</t>
-        </is>
-      </c>
-      <c r="I84">
-        <v>0.2</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">打破時空的禁錮——冷卻縮減自此突破 60% 的天塹，所有技能的冷卻如坍縮的星辰般急速消融，持續 3 秒。每級額外 −0.2% 冷卻。（不縮減自身冷卻，但仍受一般冷卻縮減加成）</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="O84">
-        <v>75</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="R84">
-        <v>3</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cdrUncap</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chronostasis</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">此技能對自身冷卻不生效，但冷卻縮減仍可作用於它。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absoluteSanctuary</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">絕對領域</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="I85">
-        <v>0.025</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">降臨絕對的領域，展開無敵結界——其間免疫一切傷害與負面效果，任何攻擊都無法觸及你分毫。基礎 0.5 秒，每級 +0.025 秒。</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="O85">
-        <v>75</v>
-      </c>
-      <c r="P85">
-        <v>0.5</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">invuln</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Absolute Sanctuary</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在絕對的領域中，任何傷害都無法觸及你分毫。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lastStandUndying</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不屈意志</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">💀</t>
-        </is>
-      </c>
-      <c r="I86">
-        <v>0.4</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">意志不屈者，縱使命懸一線亦絕不倒下——受到致命傷害時免除死亡，並獲得 1 秒無敵。觸發後進入冷卻，每級 −0.4 秒。（不受冷卻縮減影響）</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">passiveTrigger</t>
-        </is>
-      </c>
-      <c r="O86">
-        <v>90</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">undyingGuard</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Last Undying Stand</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">意志不屈者，縱使命懸一線也絕不倒下。（此技能不受冷卻縮減影響）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">timeBarrier</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">時間結界</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⏱️</t>
-        </is>
-      </c>
-      <c r="I87">
-        <v>1</v>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">編織拖曳時光的結界，敵人的動作被無情延緩，攻速大幅降低，持續 8 秒。每級敵人攻速 −1%。（敵降低後攻速 = 原攻速 /(1+降低%)）</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="O87">
-        <v>45</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <v>8</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">enemySlow</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Barrier</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">結界之內，敵人的時間被無情拖曳。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dualCoreFusion</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">混沌雙修</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">☯️</t>
-        </is>
-      </c>
-      <c r="I88">
-        <v>0.6</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雙核交融，物理與魔法的界限就此崩解——所有物理技能汲取魔攻之力、所有魔法技能承載物攻之威。每級 +0.6%。</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">passive</t>
-        </is>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">crossCore</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dual-Core Fusion</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雙核交融，物理與魔法在你手中不再涇渭分明。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">omegaImpact</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必殺一擊</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🎯</t>
-        </is>
-      </c>
-      <c r="I89">
-        <v>3</v>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">凝聚全身之力於一擊，依你的爆擊率轟出毀天滅地的必殺——造成「爆擊率% × 必殺傷害加成%」的物理傷害；爆擊率愈高，此擊愈是無可匹敵。必殺傷害加成 = 100% + 每級 +3%。</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="O89">
-        <v>60</v>
-      </c>
-      <c r="P89">
-        <v>100</v>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">phys</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">omega</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Omega Impact</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆擊率愈高，這一擊便愈是毀天滅地。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sacredInversion</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">聖療逆轉</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="I90">
-        <v>0.5</v>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">聖療之光賜福於身，生命與法力回復大幅提升；滿溢的療癒之力逆轉為裁決，化作同等傷害傾瀉於敵，持續 6 秒。每級 +0.5%。</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="O90">
-        <v>45</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="R90">
-        <v>6</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sacredInvert</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sacred Inversion</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">滿溢的聖光既能療癒自身，亦能化為裁決敵人的利刃。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潛力天賦</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chronosStasis</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">時空凝滯</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="I91">
-        <v>0.5</v>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">封鎖周遭的時空，令萬物靜止——唯有承神之賜福者能自由行動；凝滯之間你的所有傷害大幅提升，敵人動彈不得，持續 8 秒。每級 +0.5% 所有傷害。</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="O91">
-        <v>120</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="R91">
-        <v>8</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">timeStop</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chronos Stasis</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">唯有獲得神之賜福者，方能在凝滯的時空中行動自如。</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -1652,33 +1652,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">t5_allres</t>
+          <t xml:space="preserve">t5_earth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">全域壁壘</t>
+          <t xml:space="preserve">磐岩共鳴</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧿</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemRes</t>
+          <t xml:space="preserve">elemEarth</t>
         </is>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">全屬性抗性額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -1693,22 +1693,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">t5_global</t>
+          <t xml:space="preserve">t5_allres</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">傷害偏折</t>
+          <t xml:space="preserve">全域壁壘</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🧿</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">globalDmgRed</t>
+          <t xml:space="preserve">elemRes</t>
         </is>
       </c>
       <c r="G41">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局減傷額外提高</t>
+          <t xml:space="preserve">全屬性抗性額外提高</t>
         </is>
       </c>
     </row>
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vsfire</t>
+          <t xml:space="preserve">t5_global</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">滅焰打擊</t>
+          <t xml:space="preserve">傷害偏折</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsFire</t>
+          <t xml:space="preserve">globalDmgRed</t>
         </is>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">對火屬性敵人傷害提高</t>
+          <t xml:space="preserve">全局減傷額外提高</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1775,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vsice</t>
+          <t xml:space="preserve">t6_vsfire</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">碎冰打擊</t>
+          <t xml:space="preserve">滅焰打擊</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsIce</t>
+          <t xml:space="preserve">dmgVsFire</t>
         </is>
       </c>
       <c r="G43">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">對冰屬性敵人傷害提高</t>
+          <t xml:space="preserve">對火屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1816,22 +1816,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vslightning</t>
+          <t xml:space="preserve">t6_vsice</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">斷雷打擊</t>
+          <t xml:space="preserve">碎冰打擊</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLightning</t>
+          <t xml:space="preserve">dmgVsIce</t>
         </is>
       </c>
       <c r="G44">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">對電屬性敵人傷害提高</t>
+          <t xml:space="preserve">對冰屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1857,22 +1857,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vspoison</t>
+          <t xml:space="preserve">t6_vslightning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">淨毒打擊</t>
+          <t xml:space="preserve">斷雷打擊</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsPoison</t>
+          <t xml:space="preserve">dmgVsLightning</t>
         </is>
       </c>
       <c r="G45">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">對毒屬性敵人傷害提高</t>
+          <t xml:space="preserve">對電屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1898,22 +1898,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vsdark</t>
+          <t xml:space="preserve">t6_vspoison</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">驅暗打擊</t>
+          <t xml:space="preserve">淨毒打擊</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsDark</t>
+          <t xml:space="preserve">dmgVsPoison</t>
         </is>
       </c>
       <c r="G46">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">對暗屬性敵人傷害提高</t>
+          <t xml:space="preserve">對毒屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vslight</t>
+          <t xml:space="preserve">t6_vsdark</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">蝕聖打擊</t>
+          <t xml:space="preserve">驅暗打擊</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLight</t>
+          <t xml:space="preserve">dmgVsDark</t>
         </is>
       </c>
       <c r="G47">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">對聖屬性敵人傷害提高</t>
+          <t xml:space="preserve">對暗屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1980,33 +1980,33 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_boss</t>
+          <t xml:space="preserve">t6_vslight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">弒王進階</t>
+          <t xml:space="preserve">蝕聖打擊</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmg</t>
+          <t xml:space="preserve">dmgVsLight</t>
         </is>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 傷害額外提高</t>
+          <t xml:space="preserve">對聖屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -2021,33 +2021,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_bossred</t>
+          <t xml:space="preserve">t6_vsearth</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠龍血鎧</t>
+          <t xml:space="preserve">裂地打擊</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">🐉</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmgRed</t>
+          <t xml:space="preserve">dmgVsEarth</t>
         </is>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
+          <t xml:space="preserve">對地屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -2058,37 +2058,37 @@
         </is>
       </c>
       <c r="B50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_patk</t>
+          <t xml:space="preserve">t6_boss</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">武力賁張</t>
+          <t xml:space="preserve">弒王進階</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">👑</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">patkPct</t>
+          <t xml:space="preserve">bossDmg</t>
         </is>
       </c>
       <c r="G50">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理攻擊總值額外提高</t>
+          <t xml:space="preserve">對 BOSS 傷害額外提高</t>
         </is>
       </c>
     </row>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_matk</t>
+          <t xml:space="preserve">t6_bossred</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">奧能賁張</t>
+          <t xml:space="preserve">屠龍血鎧</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪄</t>
+          <t xml:space="preserve">🐉</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">matkPct</t>
+          <t xml:space="preserve">bossDmgRed</t>
         </is>
       </c>
       <c r="G51">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法攻擊總值額外提高</t>
+          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
         </is>
       </c>
     </row>
@@ -2144,33 +2144,33 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_allres</t>
+          <t xml:space="preserve">t7_patk</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象壁壘</t>
+          <t xml:space="preserve">武力賁張</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌈</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemRes</t>
+          <t xml:space="preserve">patkPct</t>
         </is>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">全屬性抗性額外提高</t>
+          <t xml:space="preserve">物理攻擊總值額外提高</t>
         </is>
       </c>
     </row>
@@ -2185,33 +2185,33 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_evasion</t>
+          <t xml:space="preserve">t7_matk</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">無影迷蹤</t>
+          <t xml:space="preserve">奧能賁張</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">💨</t>
+          <t xml:space="preserve">🪄</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">evasion</t>
+          <t xml:space="preserve">matkPct</t>
         </is>
       </c>
       <c r="G53">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="H53">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃避率提高</t>
+          <t xml:space="preserve">魔法攻擊總值額外提高</t>
         </is>
       </c>
     </row>
@@ -2226,33 +2226,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_hit</t>
+          <t xml:space="preserve">t7_allres</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">天眼鎖定</t>
+          <t xml:space="preserve">萬象壁壘</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">🎯</t>
+          <t xml:space="preserve">🌈</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">hit</t>
+          <t xml:space="preserve">elemRes</t>
         </is>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">命中率提高</t>
+          <t xml:space="preserve">全屬性抗性額外提高</t>
         </is>
       </c>
     </row>
@@ -2267,33 +2267,33 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_global</t>
+          <t xml:space="preserve">t7_evasion</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">絕對偏折</t>
+          <t xml:space="preserve">無影迷蹤</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕳️</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">globalDmgRed</t>
+          <t xml:space="preserve">evasion</t>
         </is>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局減傷額外提高</t>
+          <t xml:space="preserve">閃避率提高</t>
         </is>
       </c>
     </row>
@@ -2308,36 +2308,33 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_potential</t>
+          <t xml:space="preserve">t7_hit</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">潛力爆發</t>
+          <t xml:space="preserve">天眼鎖定</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">💥</t>
+          <t xml:space="preserve">🎯</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">potentialUnlock</t>
+          <t xml:space="preserve">hit</t>
         </is>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H56">
-        <v>4</v>
-      </c>
-      <c r="J56">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">解鎖新類型技能「潛力」三個並給予技能點</t>
+          <t xml:space="preserve">命中率提高</t>
         </is>
       </c>
     </row>
@@ -2352,33 +2349,33 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_totaldmg</t>
+          <t xml:space="preserve">t7_global</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">破壞本源</t>
+          <t xml:space="preserve">絕對偏折</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
+          <t xml:space="preserve">🕳️</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">totalDmgPct</t>
+          <t xml:space="preserve">globalDmgRed</t>
         </is>
       </c>
       <c r="G57">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">總傷害額外增加</t>
+          <t xml:space="preserve">全局減傷額外提高</t>
         </is>
       </c>
     </row>
@@ -2389,37 +2386,40 @@
         </is>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvsfire</t>
+          <t xml:space="preserve">t7_potential</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦焰之心</t>
+          <t xml:space="preserve">潛力爆發</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">💥</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsFire</t>
+          <t xml:space="preserve">potentialUnlock</t>
         </is>
       </c>
       <c r="G58">
+        <v>2</v>
+      </c>
+      <c r="H58">
+        <v>4</v>
+      </c>
+      <c r="J58">
         <v>3</v>
       </c>
-      <c r="H58">
-        <v>6</v>
-      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">對火屬性敵人抗性提高</t>
+          <t xml:space="preserve">解鎖新類型技能「潛力」三個並給予技能點</t>
         </is>
       </c>
     </row>
@@ -2430,37 +2430,37 @@
         </is>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvsice</t>
+          <t xml:space="preserve">t7_totaldmg</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦冰之心</t>
+          <t xml:space="preserve">破壞本源</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">☄️</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsIce</t>
+          <t xml:space="preserve">totalDmgPct</t>
         </is>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="H59">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">對冰屬性敵人抗性提高</t>
+          <t xml:space="preserve">總傷害額外增加</t>
         </is>
       </c>
     </row>
@@ -2475,22 +2475,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvslightning</t>
+          <t xml:space="preserve">t8_rvsfire</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦雷之心</t>
+          <t xml:space="preserve">禦焰之心</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsLightning</t>
+          <t xml:space="preserve">resVsFire</t>
         </is>
       </c>
       <c r="G60">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">對電屬性敵人抗性提高</t>
+          <t xml:space="preserve">對火屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2516,22 +2516,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvspoison</t>
+          <t xml:space="preserve">t8_rvsice</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦毒之心</t>
+          <t xml:space="preserve">禦冰之心</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsPoison</t>
+          <t xml:space="preserve">resVsIce</t>
         </is>
       </c>
       <c r="G61">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">對毒屬性敵人抗性提高</t>
+          <t xml:space="preserve">對冰屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2557,22 +2557,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvsdark</t>
+          <t xml:space="preserve">t8_rvslightning</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦暗之心</t>
+          <t xml:space="preserve">禦雷之心</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsDark</t>
+          <t xml:space="preserve">resVsLightning</t>
         </is>
       </c>
       <c r="G62">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">對暗屬性敵人抗性提高</t>
+          <t xml:space="preserve">對電屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2598,22 +2598,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvslight</t>
+          <t xml:space="preserve">t8_rvspoison</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦聖之心</t>
+          <t xml:space="preserve">禦毒之心</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsLight</t>
+          <t xml:space="preserve">resVsPoison</t>
         </is>
       </c>
       <c r="G63">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">對聖屬性敵人抗性提高</t>
+          <t xml:space="preserve">對毒屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2639,33 +2639,33 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_boss</t>
+          <t xml:space="preserve">t8_rvsdark</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">弒王極意</t>
+          <t xml:space="preserve">禦暗之心</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmg</t>
+          <t xml:space="preserve">resVsDark</t>
         </is>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 傷害額外提高</t>
+          <t xml:space="preserve">對暗屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2680,33 +2680,33 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_bossred</t>
+          <t xml:space="preserve">t8_rvslight</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠龍聖鎧</t>
+          <t xml:space="preserve">禦聖之心</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">🐉</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmgRed</t>
+          <t xml:space="preserve">resVsLight</t>
         </is>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
+          <t xml:space="preserve">對聖屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2717,37 +2717,37 @@
         </is>
       </c>
       <c r="B66">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_fire</t>
+          <t xml:space="preserve">t8_rvsearth</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">烈焰霸體</t>
+          <t xml:space="preserve">禦地之心</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemFire</t>
+          <t xml:space="preserve">resVsEarth</t>
         </is>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外附加</t>
+          <t xml:space="preserve">對地屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2758,37 +2758,37 @@
         </is>
       </c>
       <c r="B67">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_ice</t>
+          <t xml:space="preserve">t8_boss</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜霸體</t>
+          <t xml:space="preserve">弒王極意</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">👑</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemIce</t>
+          <t xml:space="preserve">bossDmg</t>
         </is>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外附加</t>
+          <t xml:space="preserve">對 BOSS 傷害額外提高</t>
         </is>
       </c>
     </row>
@@ -2799,37 +2799,37 @@
         </is>
       </c>
       <c r="B68">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_lightning</t>
+          <t xml:space="preserve">t8_bossred</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷霆霸體</t>
+          <t xml:space="preserve">屠龍聖鎧</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🐉</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemLightning</t>
+          <t xml:space="preserve">bossDmgRed</t>
         </is>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H68">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外附加</t>
+          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
         </is>
       </c>
     </row>
@@ -2844,22 +2844,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_poison</t>
+          <t xml:space="preserve">t9_fire</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒脈霸體</t>
+          <t xml:space="preserve">烈焰霸體</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemPoison</t>
+          <t xml:space="preserve">elemFire</t>
         </is>
       </c>
       <c r="G69">
@@ -2885,22 +2885,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_light</t>
+          <t xml:space="preserve">t9_ice</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖輝霸體</t>
+          <t xml:space="preserve">寒霜霸體</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemLight</t>
+          <t xml:space="preserve">elemIce</t>
         </is>
       </c>
       <c r="G70">
@@ -2926,22 +2926,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_dark</t>
+          <t xml:space="preserve">t9_lightning</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗影霸體</t>
+          <t xml:space="preserve">雷霆霸體</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDark</t>
+          <t xml:space="preserve">elemLightning</t>
         </is>
       </c>
       <c r="G71">
@@ -2967,22 +2967,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_pres</t>
+          <t xml:space="preserve">t9_poison</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">不壞金身</t>
+          <t xml:space="preserve">毒脈霸體</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">pRes</t>
+          <t xml:space="preserve">elemPoison</t>
         </is>
       </c>
       <c r="G72">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理抗性總值額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -3008,22 +3008,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_mres</t>
+          <t xml:space="preserve">t9_light</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">不滅法身</t>
+          <t xml:space="preserve">聖輝霸體</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌌</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">mRes</t>
+          <t xml:space="preserve">elemLight</t>
         </is>
       </c>
       <c r="G73">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法抗性總值額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -3045,37 +3045,37 @@
         </is>
       </c>
       <c r="B74">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_str</t>
+          <t xml:space="preserve">t9_dark</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">力量超昇</t>
+          <t xml:space="preserve">暗影霸體</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">💪</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">strPct</t>
+          <t xml:space="preserve">elemDark</t>
         </is>
       </c>
       <c r="G74">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">力量總值額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -3086,37 +3086,37 @@
         </is>
       </c>
       <c r="B75">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_agi</t>
+          <t xml:space="preserve">t9_earth</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">迅捷超昇</t>
+          <t xml:space="preserve">磐岩霸體</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪽</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">agiPct</t>
+          <t xml:space="preserve">elemEarth</t>
         </is>
       </c>
       <c r="G75">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">敏捷總值額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -3127,37 +3127,37 @@
         </is>
       </c>
       <c r="B76">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_int</t>
+          <t xml:space="preserve">t9_pres</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">奧術超昇</t>
+          <t xml:space="preserve">不壞金身</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔮</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">intPct</t>
+          <t xml:space="preserve">pRes</t>
         </is>
       </c>
       <c r="G76">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">智力總值額外提高</t>
+          <t xml:space="preserve">物理抗性總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3168,37 +3168,37 @@
         </is>
       </c>
       <c r="B77">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_vit</t>
+          <t xml:space="preserve">t9_mres</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">鋼骨超昇</t>
+          <t xml:space="preserve">不滅法身</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">🦴</t>
+          <t xml:space="preserve">🌌</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitPct</t>
+          <t xml:space="preserve">mRes</t>
         </is>
       </c>
       <c r="G77">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐力總值額外提高</t>
+          <t xml:space="preserve">魔法抗性總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3213,33 +3213,33 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_bossred</t>
+          <t xml:space="preserve">t10_str</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠龍神鎧</t>
+          <t xml:space="preserve">力量超昇</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">🐉</t>
+          <t xml:space="preserve">💪</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmgRed</t>
+          <t xml:space="preserve">strPct</t>
         </is>
       </c>
       <c r="G78">
-        <v>10</v>
+        <v>0.75</v>
       </c>
       <c r="H78">
-        <v>20</v>
+        <v>1.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
+          <t xml:space="preserve">力量總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3254,33 +3254,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_gemeff</t>
+          <t xml:space="preserve">t10_agi</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">寶石共鳴</t>
+          <t xml:space="preserve">迅捷超昇</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">💎</t>
+          <t xml:space="preserve">🪽</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">gemEff</t>
+          <t xml:space="preserve">agiPct</t>
         </is>
       </c>
       <c r="G79">
-        <v>10</v>
+        <v>0.75</v>
       </c>
       <c r="H79">
-        <v>20</v>
+        <v>1.5</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">寶石鑲嵌效率提高</t>
+          <t xml:space="preserve">敏捷總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3295,33 +3295,33 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_totaldmg</t>
+          <t xml:space="preserve">t10_int</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">毀滅本源</t>
+          <t xml:space="preserve">奧術超昇</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
+          <t xml:space="preserve">🔮</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">totalDmgPct</t>
+          <t xml:space="preserve">intPct</t>
         </is>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">總傷害額外增幅</t>
+          <t xml:space="preserve">智力總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3336,34 +3336,198 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t xml:space="preserve">t10_vit</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鋼骨超昇</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🦴</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitPct</t>
+        </is>
+      </c>
+      <c r="G81">
+        <v>0.75</v>
+      </c>
+      <c r="H81">
+        <v>1.5</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">耐力總值額外提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轉生天賦</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>10</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t10_bossred</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠龍神鎧</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🐉</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bossDmgRed</t>
+        </is>
+      </c>
+      <c r="G82">
+        <v>10</v>
+      </c>
+      <c r="H82">
+        <v>20</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轉生天賦</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>10</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t10_gemeff</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寶石共鳴</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💎</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gemEff</t>
+        </is>
+      </c>
+      <c r="G83">
+        <v>10</v>
+      </c>
+      <c r="H83">
+        <v>20</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寶石鑲嵌效率提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轉生天賦</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>10</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t10_totaldmg</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">毀滅本源</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">totalDmgPct</t>
+        </is>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">總傷害額外增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轉生天賦</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>10</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t xml:space="preserve">t10_potential</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力昇華</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t xml:space="preserve">🌌</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t xml:space="preserve">potentialUnlock</t>
         </is>
       </c>
-      <c r="G81">
-        <v>2</v>
-      </c>
-      <c r="H81">
+      <c r="G85">
+        <v>2</v>
+      </c>
+      <c r="H85">
         <v>4</v>
       </c>
-      <c r="J81">
-        <v>1</v>
-      </c>
-      <c r="M81" t="inlineStr">
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">解鎖新類型技能「潛力」一個並給予技能點</t>
         </is>

--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -1693,33 +1693,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">t5_allres</t>
+          <t xml:space="preserve">t5_wind</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">全域壁壘</t>
+          <t xml:space="preserve">疾風共鳴</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧿</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemRes</t>
+          <t xml:space="preserve">elemWind</t>
         </is>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">全屬性抗性額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">t5_global</t>
+          <t xml:space="preserve">t5_allres</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">傷害偏折</t>
+          <t xml:space="preserve">全域壁壘</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🧿</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">globalDmgRed</t>
+          <t xml:space="preserve">elemRes</t>
         </is>
       </c>
       <c r="G42">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局減傷額外提高</t>
+          <t xml:space="preserve">全屬性抗性額外提高</t>
         </is>
       </c>
     </row>
@@ -1771,37 +1771,37 @@
         </is>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vsfire</t>
+          <t xml:space="preserve">t5_global</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">滅焰打擊</t>
+          <t xml:space="preserve">傷害偏折</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsFire</t>
+          <t xml:space="preserve">globalDmgRed</t>
         </is>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">對火屬性敵人傷害提高</t>
+          <t xml:space="preserve">全局減傷額外提高</t>
         </is>
       </c>
     </row>
@@ -1816,22 +1816,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vsice</t>
+          <t xml:space="preserve">t6_vsfire</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">碎冰打擊</t>
+          <t xml:space="preserve">滅焰打擊</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsIce</t>
+          <t xml:space="preserve">dmgVsFire</t>
         </is>
       </c>
       <c r="G44">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">對冰屬性敵人傷害提高</t>
+          <t xml:space="preserve">對火屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1857,22 +1857,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vslightning</t>
+          <t xml:space="preserve">t6_vsice</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">斷雷打擊</t>
+          <t xml:space="preserve">碎冰打擊</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLightning</t>
+          <t xml:space="preserve">dmgVsIce</t>
         </is>
       </c>
       <c r="G45">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">對電屬性敵人傷害提高</t>
+          <t xml:space="preserve">對冰屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1898,22 +1898,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vspoison</t>
+          <t xml:space="preserve">t6_vslightning</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">淨毒打擊</t>
+          <t xml:space="preserve">斷雷打擊</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsPoison</t>
+          <t xml:space="preserve">dmgVsLightning</t>
         </is>
       </c>
       <c r="G46">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">對毒屬性敵人傷害提高</t>
+          <t xml:space="preserve">對電屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vsdark</t>
+          <t xml:space="preserve">t6_vspoison</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">驅暗打擊</t>
+          <t xml:space="preserve">淨毒打擊</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsDark</t>
+          <t xml:space="preserve">dmgVsPoison</t>
         </is>
       </c>
       <c r="G47">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">對暗屬性敵人傷害提高</t>
+          <t xml:space="preserve">對毒屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -1980,22 +1980,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vslight</t>
+          <t xml:space="preserve">t6_vsdark</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">蝕聖打擊</t>
+          <t xml:space="preserve">驅暗打擊</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLight</t>
+          <t xml:space="preserve">dmgVsDark</t>
         </is>
       </c>
       <c r="G48">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">對聖屬性敵人傷害提高</t>
+          <t xml:space="preserve">對暗屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -2021,22 +2021,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_vsearth</t>
+          <t xml:space="preserve">t6_vslight</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">裂地打擊</t>
+          <t xml:space="preserve">蝕聖打擊</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsEarth</t>
+          <t xml:space="preserve">dmgVsLight</t>
         </is>
       </c>
       <c r="G49">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">對地屬性敵人傷害提高</t>
+          <t xml:space="preserve">對聖屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -2062,33 +2062,33 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_boss</t>
+          <t xml:space="preserve">t6_vsearth</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">弒王進階</t>
+          <t xml:space="preserve">裂地打擊</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmg</t>
+          <t xml:space="preserve">dmgVsEarth</t>
         </is>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 傷害額外提高</t>
+          <t xml:space="preserve">對地屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -2103,33 +2103,33 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">t6_bossred</t>
+          <t xml:space="preserve">t6_vswind</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠龍血鎧</t>
+          <t xml:space="preserve">破風打擊</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">🐉</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmgRed</t>
+          <t xml:space="preserve">dmgVsWind</t>
         </is>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
+          <t xml:space="preserve">對風屬性敵人傷害提高</t>
         </is>
       </c>
     </row>
@@ -2140,37 +2140,37 @@
         </is>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_patk</t>
+          <t xml:space="preserve">t6_boss</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">武力賁張</t>
+          <t xml:space="preserve">弒王進階</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">👑</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">patkPct</t>
+          <t xml:space="preserve">bossDmg</t>
         </is>
       </c>
       <c r="G52">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理攻擊總值額外提高</t>
+          <t xml:space="preserve">對 BOSS 傷害額外提高</t>
         </is>
       </c>
     </row>
@@ -2181,37 +2181,37 @@
         </is>
       </c>
       <c r="B53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_matk</t>
+          <t xml:space="preserve">t6_bossred</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">奧能賁張</t>
+          <t xml:space="preserve">屠龍血鎧</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪄</t>
+          <t xml:space="preserve">🐉</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">matkPct</t>
+          <t xml:space="preserve">bossDmgRed</t>
         </is>
       </c>
       <c r="G53">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法攻擊總值額外提高</t>
+          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
         </is>
       </c>
     </row>
@@ -2226,33 +2226,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_allres</t>
+          <t xml:space="preserve">t7_patk</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象壁壘</t>
+          <t xml:space="preserve">武力賁張</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌈</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemRes</t>
+          <t xml:space="preserve">patkPct</t>
         </is>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">全屬性抗性額外提高</t>
+          <t xml:space="preserve">物理攻擊總值額外提高</t>
         </is>
       </c>
     </row>
@@ -2267,33 +2267,33 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_evasion</t>
+          <t xml:space="preserve">t7_matk</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">無影迷蹤</t>
+          <t xml:space="preserve">奧能賁張</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">💨</t>
+          <t xml:space="preserve">🪄</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">evasion</t>
+          <t xml:space="preserve">matkPct</t>
         </is>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="H55">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃避率提高</t>
+          <t xml:space="preserve">魔法攻擊總值額外提高</t>
         </is>
       </c>
     </row>
@@ -2308,33 +2308,33 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_hit</t>
+          <t xml:space="preserve">t7_allres</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">天眼鎖定</t>
+          <t xml:space="preserve">萬象壁壘</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">🎯</t>
+          <t xml:space="preserve">🌈</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">hit</t>
+          <t xml:space="preserve">elemRes</t>
         </is>
       </c>
       <c r="G56">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">命中率提高</t>
+          <t xml:space="preserve">全屬性抗性額外提高</t>
         </is>
       </c>
     </row>
@@ -2349,33 +2349,33 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_global</t>
+          <t xml:space="preserve">t7_evasion</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">絕對偏折</t>
+          <t xml:space="preserve">無影迷蹤</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕳️</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">globalDmgRed</t>
+          <t xml:space="preserve">evasion</t>
         </is>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局減傷額外提高</t>
+          <t xml:space="preserve">閃避率提高</t>
         </is>
       </c>
     </row>
@@ -2390,36 +2390,33 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_potential</t>
+          <t xml:space="preserve">t7_hit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">潛力爆發</t>
+          <t xml:space="preserve">天眼鎖定</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">💥</t>
+          <t xml:space="preserve">🎯</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">potentialUnlock</t>
+          <t xml:space="preserve">hit</t>
         </is>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H58">
-        <v>4</v>
-      </c>
-      <c r="J58">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">解鎖新類型技能「潛力」三個並給予技能點</t>
+          <t xml:space="preserve">命中率提高</t>
         </is>
       </c>
     </row>
@@ -2434,33 +2431,33 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">t7_totaldmg</t>
+          <t xml:space="preserve">t7_global</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">破壞本源</t>
+          <t xml:space="preserve">絕對偏折</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
+          <t xml:space="preserve">🕳️</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">totalDmgPct</t>
+          <t xml:space="preserve">globalDmgRed</t>
         </is>
       </c>
       <c r="G59">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">總傷害額外增加</t>
+          <t xml:space="preserve">全局減傷額外提高</t>
         </is>
       </c>
     </row>
@@ -2471,37 +2468,40 @@
         </is>
       </c>
       <c r="B60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvsfire</t>
+          <t xml:space="preserve">t7_potential</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦焰之心</t>
+          <t xml:space="preserve">潛力爆發</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">💥</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsFire</t>
+          <t xml:space="preserve">potentialUnlock</t>
         </is>
       </c>
       <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60">
+        <v>4</v>
+      </c>
+      <c r="J60">
         <v>3</v>
       </c>
-      <c r="H60">
-        <v>6</v>
-      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">對火屬性敵人抗性提高</t>
+          <t xml:space="preserve">解鎖新類型技能「潛力」三個並給予技能點</t>
         </is>
       </c>
     </row>
@@ -2512,37 +2512,37 @@
         </is>
       </c>
       <c r="B61">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvsice</t>
+          <t xml:space="preserve">t7_totaldmg</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦冰之心</t>
+          <t xml:space="preserve">破壞本源</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">☄️</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsIce</t>
+          <t xml:space="preserve">totalDmgPct</t>
         </is>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="H61">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">對冰屬性敵人抗性提高</t>
+          <t xml:space="preserve">總傷害額外增加</t>
         </is>
       </c>
     </row>
@@ -2557,22 +2557,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvslightning</t>
+          <t xml:space="preserve">t8_rvsfire</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦雷之心</t>
+          <t xml:space="preserve">禦焰之心</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsLightning</t>
+          <t xml:space="preserve">resVsFire</t>
         </is>
       </c>
       <c r="G62">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">對電屬性敵人抗性提高</t>
+          <t xml:space="preserve">對火屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2598,22 +2598,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvspoison</t>
+          <t xml:space="preserve">t8_rvsice</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦毒之心</t>
+          <t xml:space="preserve">禦冰之心</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsPoison</t>
+          <t xml:space="preserve">resVsIce</t>
         </is>
       </c>
       <c r="G63">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">對毒屬性敵人抗性提高</t>
+          <t xml:space="preserve">對冰屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2639,22 +2639,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvsdark</t>
+          <t xml:space="preserve">t8_rvslightning</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦暗之心</t>
+          <t xml:space="preserve">禦雷之心</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsDark</t>
+          <t xml:space="preserve">resVsLightning</t>
         </is>
       </c>
       <c r="G64">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">對暗屬性敵人抗性提高</t>
+          <t xml:space="preserve">對電屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2680,22 +2680,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvslight</t>
+          <t xml:space="preserve">t8_rvspoison</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦聖之心</t>
+          <t xml:space="preserve">禦毒之心</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsLight</t>
+          <t xml:space="preserve">resVsPoison</t>
         </is>
       </c>
       <c r="G65">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">對聖屬性敵人抗性提高</t>
+          <t xml:space="preserve">對毒屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2721,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_rvsearth</t>
+          <t xml:space="preserve">t8_rvsdark</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">禦地之心</t>
+          <t xml:space="preserve">禦暗之心</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">resVsEarth</t>
+          <t xml:space="preserve">resVsDark</t>
         </is>
       </c>
       <c r="G66">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">對地屬性敵人抗性提高</t>
+          <t xml:space="preserve">對暗屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2762,33 +2762,33 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_boss</t>
+          <t xml:space="preserve">t8_rvslight</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">弒王極意</t>
+          <t xml:space="preserve">禦聖之心</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmg</t>
+          <t xml:space="preserve">resVsLight</t>
         </is>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 傷害額外提高</t>
+          <t xml:space="preserve">對聖屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2803,33 +2803,33 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">t8_bossred</t>
+          <t xml:space="preserve">t8_rvsearth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠龍聖鎧</t>
+          <t xml:space="preserve">禦地之心</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">🐉</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmgRed</t>
+          <t xml:space="preserve">resVsEarth</t>
         </is>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
+          <t xml:space="preserve">對地屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="B69">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_fire</t>
+          <t xml:space="preserve">t8_rvswind</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">烈焰霸體</t>
+          <t xml:space="preserve">禦風之心</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemFire</t>
+          <t xml:space="preserve">resVsWind</t>
         </is>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外附加</t>
+          <t xml:space="preserve">對風屬性敵人抗性提高</t>
         </is>
       </c>
     </row>
@@ -2881,37 +2881,37 @@
         </is>
       </c>
       <c r="B70">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_ice</t>
+          <t xml:space="preserve">t8_boss</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜霸體</t>
+          <t xml:space="preserve">弒王極意</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">👑</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemIce</t>
+          <t xml:space="preserve">bossDmg</t>
         </is>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外附加</t>
+          <t xml:space="preserve">對 BOSS 傷害額外提高</t>
         </is>
       </c>
     </row>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="B71">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_lightning</t>
+          <t xml:space="preserve">t8_bossred</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷霆霸體</t>
+          <t xml:space="preserve">屠龍聖鎧</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🐉</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemLightning</t>
+          <t xml:space="preserve">bossDmgRed</t>
         </is>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H71">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外附加</t>
+          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
         </is>
       </c>
     </row>
@@ -2967,22 +2967,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_poison</t>
+          <t xml:space="preserve">t9_fire</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒脈霸體</t>
+          <t xml:space="preserve">烈焰霸體</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemPoison</t>
+          <t xml:space="preserve">elemFire</t>
         </is>
       </c>
       <c r="G72">
@@ -3008,22 +3008,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_light</t>
+          <t xml:space="preserve">t9_ice</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖輝霸體</t>
+          <t xml:space="preserve">寒霜霸體</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemLight</t>
+          <t xml:space="preserve">elemIce</t>
         </is>
       </c>
       <c r="G73">
@@ -3049,22 +3049,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_dark</t>
+          <t xml:space="preserve">t9_lightning</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗影霸體</t>
+          <t xml:space="preserve">雷霆霸體</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDark</t>
+          <t xml:space="preserve">elemLightning</t>
         </is>
       </c>
       <c r="G74">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_earth</t>
+          <t xml:space="preserve">t9_poison</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">磐岩霸體</t>
+          <t xml:space="preserve">毒脈霸體</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemEarth</t>
+          <t xml:space="preserve">elemPoison</t>
         </is>
       </c>
       <c r="G75">
@@ -3131,22 +3131,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_pres</t>
+          <t xml:space="preserve">t9_light</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">不壞金身</t>
+          <t xml:space="preserve">聖輝霸體</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">pRes</t>
+          <t xml:space="preserve">elemLight</t>
         </is>
       </c>
       <c r="G76">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理抗性總值額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">t9_mres</t>
+          <t xml:space="preserve">t9_dark</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">不滅法身</t>
+          <t xml:space="preserve">暗影霸體</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌌</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">mRes</t>
+          <t xml:space="preserve">elemDark</t>
         </is>
       </c>
       <c r="G77">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法抗性總值額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3209,37 @@
         </is>
       </c>
       <c r="B78">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_str</t>
+          <t xml:space="preserve">t9_earth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">力量超昇</t>
+          <t xml:space="preserve">磐岩霸體</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">💪</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">strPct</t>
+          <t xml:space="preserve">elemEarth</t>
         </is>
       </c>
       <c r="G78">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">力量總值額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -3250,37 +3250,37 @@
         </is>
       </c>
       <c r="B79">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_agi</t>
+          <t xml:space="preserve">t9_wind</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">迅捷超昇</t>
+          <t xml:space="preserve">疾風霸體</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪽</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">agiPct</t>
+          <t xml:space="preserve">elemWind</t>
         </is>
       </c>
       <c r="G79">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="H79">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">敏捷總值額外提高</t>
+          <t xml:space="preserve">攻擊時額外附加</t>
         </is>
       </c>
     </row>
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="B80">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_int</t>
+          <t xml:space="preserve">t9_pres</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">奧術超昇</t>
+          <t xml:space="preserve">不壞金身</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔮</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">intPct</t>
+          <t xml:space="preserve">pRes</t>
         </is>
       </c>
       <c r="G80">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="H80">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">智力總值額外提高</t>
+          <t xml:space="preserve">物理抗性總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3332,37 +3332,37 @@
         </is>
       </c>
       <c r="B81">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_vit</t>
+          <t xml:space="preserve">t9_mres</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">鋼骨超昇</t>
+          <t xml:space="preserve">不滅法身</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">🦴</t>
+          <t xml:space="preserve">🌌</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitPct</t>
+          <t xml:space="preserve">mRes</t>
         </is>
       </c>
       <c r="G81">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="H81">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐力總值額外提高</t>
+          <t xml:space="preserve">魔法抗性總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3377,33 +3377,33 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_bossred</t>
+          <t xml:space="preserve">t10_str</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠龍神鎧</t>
+          <t xml:space="preserve">力量超昇</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">🐉</t>
+          <t xml:space="preserve">💪</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">bossDmgRed</t>
+          <t xml:space="preserve">strPct</t>
         </is>
       </c>
       <c r="G82">
-        <v>10</v>
+        <v>0.75</v>
       </c>
       <c r="H82">
-        <v>20</v>
+        <v>1.5</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
+          <t xml:space="preserve">力量總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3418,33 +3418,33 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_gemeff</t>
+          <t xml:space="preserve">t10_agi</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">寶石共鳴</t>
+          <t xml:space="preserve">迅捷超昇</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">💎</t>
+          <t xml:space="preserve">🪽</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">gemEff</t>
+          <t xml:space="preserve">agiPct</t>
         </is>
       </c>
       <c r="G83">
-        <v>10</v>
+        <v>0.75</v>
       </c>
       <c r="H83">
-        <v>20</v>
+        <v>1.5</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">寶石鑲嵌效率提高</t>
+          <t xml:space="preserve">敏捷總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3459,33 +3459,33 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">t10_totaldmg</t>
+          <t xml:space="preserve">t10_int</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">毀滅本源</t>
+          <t xml:space="preserve">奧術超昇</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
+          <t xml:space="preserve">🔮</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">totalDmgPct</t>
+          <t xml:space="preserve">intPct</t>
         </is>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H84">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">總傷害額外增幅</t>
+          <t xml:space="preserve">智力總值額外提高</t>
         </is>
       </c>
     </row>
@@ -3500,34 +3500,198 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t xml:space="preserve">t10_vit</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鋼骨超昇</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🦴</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitPct</t>
+        </is>
+      </c>
+      <c r="G85">
+        <v>0.75</v>
+      </c>
+      <c r="H85">
+        <v>1.5</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">耐力總值額外提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轉生天賦</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t10_bossred</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠龍神鎧</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🐉</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bossDmgRed</t>
+        </is>
+      </c>
+      <c r="G86">
+        <v>10</v>
+      </c>
+      <c r="H86">
+        <v>20</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對 BOSS 敵人抗性額外提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轉生天賦</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>10</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t10_gemeff</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寶石共鳴</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💎</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gemEff</t>
+        </is>
+      </c>
+      <c r="G87">
+        <v>10</v>
+      </c>
+      <c r="H87">
+        <v>20</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寶石鑲嵌效率提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轉生天賦</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>10</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t10_totaldmg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">毀滅本源</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">totalDmgPct</t>
+        </is>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">總傷害額外增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轉生天賦</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>10</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
           <t xml:space="preserve">t10_potential</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力昇華</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t xml:space="preserve">🌌</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t xml:space="preserve">potentialUnlock</t>
         </is>
       </c>
-      <c r="G85">
-        <v>2</v>
-      </c>
-      <c r="H85">
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89">
         <v>4</v>
       </c>
-      <c r="J85">
-        <v>1</v>
-      </c>
-      <c r="M85" t="inlineStr">
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">解鎖新類型技能「潛力」一個並給予技能點</t>
         </is>
